--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2024/A320_Airline_Cumulative_Statistics_2024.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2024/A320_Airline_Cumulative_Statistics_2024.xlsx
@@ -212,13 +212,13 @@
         <v>917</v>
       </c>
       <c r="K2" s="0">
-        <v>5422</v>
+        <v>5421.9799999999996</v>
       </c>
       <c r="L2" s="0">
         <v>29.699999999999999</v>
       </c>
       <c r="M2" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.079000000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -253,13 +253,13 @@
         <v>687</v>
       </c>
       <c r="K3" s="0">
-        <v>5077</v>
+        <v>5077.1700000000001</v>
       </c>
       <c r="L3" s="0">
         <v>33.850000000000001</v>
       </c>
       <c r="M3" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.10199999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -294,13 +294,13 @@
         <v>818</v>
       </c>
       <c r="K4" s="0">
-        <v>5777</v>
+        <v>5777.4200000000001</v>
       </c>
       <c r="L4" s="0">
         <v>36.810000000000002</v>
       </c>
       <c r="M4" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.104</v>
       </c>
     </row>
     <row r="5">
@@ -335,13 +335,13 @@
         <v>839</v>
       </c>
       <c r="K5" s="0">
-        <v>4237</v>
+        <v>4236.6999999999998</v>
       </c>
       <c r="L5" s="0">
         <v>23.109999999999999</v>
       </c>
       <c r="M5" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.068000000000000005</v>
       </c>
     </row>
     <row r="6">
@@ -376,13 +376,13 @@
         <v>1155</v>
       </c>
       <c r="K6" s="0">
-        <v>5951</v>
+        <v>5951.0299999999997</v>
       </c>
       <c r="L6" s="0">
         <v>36.909999999999997</v>
       </c>
       <c r="M6" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.097000000000000003</v>
       </c>
     </row>
     <row r="7">
@@ -417,13 +417,13 @@
         <v>922</v>
       </c>
       <c r="K7" s="0">
-        <v>4829</v>
+        <v>4829.0500000000002</v>
       </c>
       <c r="L7" s="0">
         <v>26.789999999999999</v>
       </c>
       <c r="M7" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.072999999999999995</v>
       </c>
     </row>
     <row r="8">
@@ -458,13 +458,13 @@
         <v>933</v>
       </c>
       <c r="K8" s="0">
-        <v>5868</v>
+        <v>5868.0900000000001</v>
       </c>
       <c r="L8" s="0">
         <v>39.119999999999997</v>
       </c>
       <c r="M8" s="0">
-        <v>0.11</v>
+        <v>0.109</v>
       </c>
     </row>
     <row r="9">
@@ -499,13 +499,13 @@
         <v>940</v>
       </c>
       <c r="K9" s="0">
-        <v>5557</v>
+        <v>5556.8699999999999</v>
       </c>
       <c r="L9" s="0">
         <v>33.880000000000003</v>
       </c>
       <c r="M9" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.091999999999999998</v>
       </c>
     </row>
   </sheetData>
